--- a/CHIK_MORBID/03_Output/tables/core3_rr_tables.xlsx
+++ b/CHIK_MORBID/03_Output/tables/core3_rr_tables.xlsx
@@ -797,58 +797,58 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>2.27727978218592</v>
+        <v>2.2890443040815</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9300509476095</v>
+        <v>1.93993329568904</v>
       </c>
       <c r="D2" t="n">
-        <v>2.68697736335714</v>
+        <v>2.70098143977001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.24939272724085</v>
+        <v>2.25818740040097</v>
       </c>
       <c r="F2" t="n">
-        <v>1.90485143448898</v>
+        <v>1.91974796726206</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64478405486613</v>
+        <v>2.62631031730998</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00189060150444287</v>
+        <v>0.00207235618528276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0016757826917479</v>
+        <v>0.00183657240661529</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00219917537189214</v>
+        <v>0.00240877602408511</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000840494183851085</v>
+        <v>0.000917707797375357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000795830344507987</v>
+        <v>0.00087549215342858</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000917569026332035</v>
+        <v>0.0010046584953906</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00105010732059178</v>
+        <v>0.0011546483879074</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000808899845603553</v>
+        <v>0.000888800229953645</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00135826075520026</v>
+        <v>0.00148123352390697</v>
       </c>
       <c r="Q2" t="n">
-        <v>49767</v>
+        <v>45529</v>
       </c>
       <c r="R2" t="n">
         <v>266</v>
       </c>
       <c r="S2" t="n">
-        <v>1025029</v>
+        <v>938418</v>
       </c>
       <c r="T2" t="n">
         <v>784</v>
@@ -859,58 +859,58 @@
         <v>21</v>
       </c>
       <c r="B3" t="n">
-        <v>2.22340365254515</v>
+        <v>2.21375544812653</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9080973857837</v>
+        <v>1.8999492055258</v>
       </c>
       <c r="D3" t="n">
-        <v>2.59081315187731</v>
+        <v>2.57939168576544</v>
       </c>
       <c r="E3" t="n">
-        <v>2.20299132720251</v>
+        <v>2.19152509076285</v>
       </c>
       <c r="F3" t="n">
-        <v>1.90736022175346</v>
+        <v>1.88359330880052</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5806056086974</v>
+        <v>2.56896936945484</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00164181821607148</v>
+        <v>0.00178676673071709</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00150189529577062</v>
+        <v>0.0016292622563878</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00187737425507857</v>
+        <v>0.00204291446535219</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000745267671187958</v>
+        <v>0.000815307448793628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000696078600679074</v>
+        <v>0.000762854995126855</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000825744403770433</v>
+        <v>0.000902269876184967</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000896550544883523</v>
+        <v>0.000971459281923459</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0007219377327675</v>
+        <v>0.000774462763501242</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00114171648342081</v>
+        <v>0.00123684651663293</v>
       </c>
       <c r="Q3" t="n">
-        <v>120904</v>
+        <v>110350</v>
       </c>
       <c r="R3" t="n">
         <v>459</v>
       </c>
       <c r="S3" t="n">
-        <v>953892</v>
+        <v>873597</v>
       </c>
       <c r="T3" t="n">
         <v>591</v>
@@ -921,58 +921,58 @@
         <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>4.23975898355528</v>
+        <v>4.35766358494152</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2422175622051</v>
+        <v>3.32940279290789</v>
       </c>
       <c r="D4" t="n">
-        <v>5.54421654122809</v>
+        <v>5.70349492106367</v>
       </c>
       <c r="E4" t="n">
-        <v>4.10102165841086</v>
+        <v>4.19871655799701</v>
       </c>
       <c r="F4" t="n">
-        <v>3.12023088231954</v>
+        <v>3.28395807609027</v>
       </c>
       <c r="G4" t="n">
-        <v>5.23779198836911</v>
+        <v>5.2995642499334</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0038183467857592</v>
+        <v>0.00426887621795772</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00298702802012929</v>
+        <v>0.00339636135558006</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00492180112397596</v>
+        <v>0.00550010109634674</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000931072084910375</v>
+        <v>0.00101670978714367</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000892465045693486</v>
+        <v>0.000973827846682193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0010107800001709</v>
+        <v>0.00110267749024581</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00288727470084883</v>
+        <v>0.00325216643081406</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00203633120543476</v>
+        <v>0.00235354268085563</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00396898501775358</v>
+        <v>0.00446440427119146</v>
       </c>
       <c r="Q4" t="n">
-        <v>4899</v>
+        <v>4412</v>
       </c>
       <c r="R4" t="n">
         <v>66</v>
       </c>
       <c r="S4" t="n">
-        <v>1069897</v>
+        <v>979535</v>
       </c>
       <c r="T4" t="n">
         <v>984</v>
